--- a/output/pdf_financials_xlsx/RTH.xlsx
+++ b/output/pdf_financials_xlsx/RTH.xlsx
@@ -1240,7 +1240,7 @@
         <v>2.031774</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.770076</v>
+        <v>-1.770076</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
@@ -1255,43 +1255,43 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.148848</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.242036</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-19.700124</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-17.633606</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-11.895228</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.94442</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.293072</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-13.938806</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.467764000000001</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.230958</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.65219</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.491546</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.063548</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -1473,46 +1473,46 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.074424</v>
+        <v>-2.074424</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7.121018</v>
+        <v>-7.121018</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9.850061999999999</v>
+        <v>-9.850061999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8.816803</v>
+        <v>-8.816803</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.947614</v>
+        <v>-5.947614</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.47221</v>
+        <v>-7.47221</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.646536</v>
+        <v>-3.646536</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>6.969403</v>
+        <v>-6.969403</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.233882</v>
+        <v>-4.233882</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.615479</v>
+        <v>-3.615479</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.326095</v>
+        <v>-2.326095</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.245773</v>
+        <v>-2.245773</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.031774</v>
+        <v>-2.031774</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.770076</v>
+        <v>-1.770076</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
@@ -1635,46 +1635,46 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.074424</v>
+        <v>-2.074424</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7.121018</v>
+        <v>-7.121018</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9.850061999999999</v>
+        <v>-9.850061999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8.816803</v>
+        <v>-8.816803</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.947614</v>
+        <v>-5.947614</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.47221</v>
+        <v>-7.47221</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.646536</v>
+        <v>-3.646536</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>6.969403</v>
+        <v>-6.969403</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4.233882</v>
+        <v>-4.233882</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.615479</v>
+        <v>-3.615479</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.326095</v>
+        <v>-2.326095</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.245773</v>
+        <v>-2.245773</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.031774</v>
+        <v>-2.031774</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.770076</v>
+        <v>-1.770076</v>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>80.152755</v>
+        <v>-80.152755</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>99.12690000000001</v>
+        <v>-99.12690000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>124.536833</v>
+        <v>-124.536833</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>121.5512</v>
+        <v>-121.5512</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>174.235075</v>
+        <v>-174.235075</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>141.1294</v>
+        <v>-141.1294</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>180.77395</v>
+        <v>-180.77395</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>2.031774</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.770076</v>
+        <v>-1.770076</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>2.033682</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.771953</v>
+        <v>-1.768199</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2121,46 +2121,46 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
@@ -5442,46 +5442,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.285014</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.163277</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.392362</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.228473</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.448794</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.728722</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.349745</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.282522</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.186052</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.635284</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.886863</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.885754</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.887607</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.856013</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>2.074424</v>
+        <v>-2.074424</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>7.121018</v>
+        <v>-7.121018</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>9.850061999999999</v>
+        <v>-9.850061999999999</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-8.816803</v>
@@ -8939,7 +8939,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12034,7 +12038,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -13510,7 +13518,11 @@
           <t>Reserves 2,448,794</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -14238,7 +14250,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -15423,7 +15439,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.285014</v>
       </c>
@@ -30755,10 +30775,10 @@
         </is>
       </c>
       <c r="Q260" s="5" t="n">
-        <v>2.031774</v>
+        <v>-2.031774</v>
       </c>
       <c r="R260" s="5" t="n">
-        <v>1.770076</v>
+        <v>-1.770076</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -31546,25 +31566,25 @@
         </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>8.816803</v>
+        <v>-8.816803</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>5.947614</v>
+        <v>-5.947614</v>
       </c>
       <c r="J270" s="5" t="n">
-        <v>7.47221</v>
+        <v>-7.47221</v>
       </c>
       <c r="K270" s="5" t="n">
-        <v>3.646536</v>
+        <v>-3.646536</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>6.969403</v>
+        <v>-6.969403</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>4.233882</v>
+        <v>-4.233882</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>3.615479</v>
+        <v>-3.615479</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -31572,10 +31592,10 @@
         </is>
       </c>
       <c r="P270" s="5" t="n">
-        <v>2.245773</v>
+        <v>-2.245773</v>
       </c>
       <c r="Q270" s="5" t="n">
-        <v>2.031774</v>
+        <v>-2.031774</v>
       </c>
       <c r="R270" t="inlineStr">
         <is>
@@ -31660,10 +31680,10 @@
         </is>
       </c>
       <c r="O271" s="5" t="n">
-        <v>2.326095</v>
+        <v>-2.326095</v>
       </c>
       <c r="P271" s="5" t="n">
-        <v>2.245773</v>
+        <v>-2.245773</v>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -37718,10 +37738,10 @@
         </is>
       </c>
       <c r="G339" s="5" t="n">
-        <v>9.850061999999999</v>
+        <v>-9.850061999999999</v>
       </c>
       <c r="H339" s="5" t="n">
-        <v>6.601013</v>
+        <v>-6.601013</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -40077,10 +40097,10 @@
         </is>
       </c>
       <c r="F365" s="5" t="n">
-        <v>7.121018</v>
+        <v>-7.121018</v>
       </c>
       <c r="G365" s="5" t="n">
-        <v>9.850061999999999</v>
+        <v>-9.850061999999999</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
@@ -42709,10 +42729,10 @@
         </is>
       </c>
       <c r="E394" s="5" t="n">
-        <v>2.074424</v>
+        <v>-2.074424</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>7.121018</v>
+        <v>-7.121018</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RTH.xlsx
+++ b/output/pdf_financials_xlsx/RTH.xlsx
@@ -985,46 +985,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006379</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.193033</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.087006</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0581</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051391</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025987</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00651</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012227</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004986</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002812</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003347</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002292</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003632</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000381</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -1877,46 +1877,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.074424</v>
+        <v>2.080803</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.121018</v>
+        <v>7.314051</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.850061999999999</v>
+        <v>9.937068</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8.816803</v>
+        <v>8.874903</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.947614</v>
+        <v>5.999005</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.47221</v>
+        <v>7.498197</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.646536</v>
+        <v>3.653046</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6.969403</v>
+        <v>6.98163</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.233882</v>
+        <v>4.238868</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.615479</v>
+        <v>3.618291</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.326095</v>
+        <v>2.329442</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.245773</v>
+        <v>2.248065</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.031774</v>
+        <v>2.035406</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.770076</v>
+        <v>-1.769695</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -1985,46 +1985,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.074424</v>
+        <v>2.080803</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.121018</v>
+        <v>7.314051</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.850061999999999</v>
+        <v>9.937068</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8.816803</v>
+        <v>8.874903</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.947614</v>
+        <v>5.999005</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.47221</v>
+        <v>7.498197</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.646536</v>
+        <v>3.653046</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>6.969403</v>
+        <v>6.98163</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.233882</v>
+        <v>4.238868</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.615479</v>
+        <v>3.618291</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.328158</v>
+        <v>2.331505</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.247684</v>
+        <v>2.249976</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.033682</v>
+        <v>2.037314</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.768199</v>
+        <v>-1.767818</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2282,28 +2282,28 @@
         <v>0.085572</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.561314</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.981572</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.035855</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.055574</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.611928</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.076289</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.05033</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.006297</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2390,28 +2390,28 @@
         <v>0.085572</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.561314</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.32</v>
+        <v>2.301572</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.365855</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.616</v>
+        <v>0.671574</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.611928</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.076289</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.05033</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.006297</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>0.101452</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.693303</v>
+        <v>0.131989</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3050,16 +3050,16 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.682088</v>
+        <v>0.07016</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.178732</v>
+        <v>0.102443</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.098313</v>
+        <v>0.047983</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.060979</v>
+        <v>0.054682</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -30363,7 +30363,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -37259,7 +37259,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -39526,7 +39526,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -39619,7 +39619,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -42256,7 +42256,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" s="5" t="n">
@@ -42349,7 +42349,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E390" s="5" t="n">

--- a/output/pdf_financials_xlsx/RTH.xlsx
+++ b/output/pdf_financials_xlsx/RTH.xlsx
@@ -6427,13 +6427,13 @@
         <v>-0.124889</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.034445</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001217</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014985</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003495</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001765</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -7697,13 +7697,13 @@
         <v>-0.124889</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.034445</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001217</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014985</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003495</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001765</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -7751,13 +7751,13 @@
         <v>-6.121704</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-8.705043999999999</v>
+        <v>-8.739489000000001</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-6.559426</v>
+        <v>-6.560643</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-5.26666</v>
+        <v>-5.281645</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-5.911023</v>
@@ -7766,7 +7766,7 @@
         <v>-1.568331</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-5.159989</v>
+        <v>-5.163484</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.691601</v>
@@ -7775,7 +7775,7 @@
         <v>-1.500151</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.252571</v>
+        <v>-1.254336</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-1.003405</v>
@@ -17688,7 +17688,11 @@
           <t>Acquisition of equipment 3</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19011,7 +19015,11 @@
           <t>Acquisition of equipment (note 3)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -23074,7 +23082,11 @@
           <t>Acquisition of equipment (note 6)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -25679,7 +25691,11 @@
           <t>Proceeds from private placement (note 7(b))</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27119,7 +27135,11 @@
           <t>Acquisition of equipment (note 7)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -27754,7 +27774,11 @@
           <t>Proceeds from private placement (note 10)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -28937,7 +28961,11 @@
           <t>Proceeds from private placement (note 8)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
